--- a/docs/source/特殊收费(1).xlsx
+++ b/docs/source/特殊收费(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27915" windowHeight="12345"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="各医院特殊收费" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="352">
   <si>
     <t>医院序号</t>
   </si>
@@ -1671,6 +1671,9 @@
     <t>固定50元</t>
   </si>
   <si>
+    <t>小腔包</t>
+  </si>
+  <si>
     <t>黑龙江省医院（南岗院区）</t>
   </si>
   <si>
@@ -1768,42 +1771,40 @@
     <t>0元</t>
   </si>
   <si>
+    <t>和名字无关（根据包类型）</t>
+  </si>
+  <si>
+    <t>额外包（棉布包装）</t>
+  </si>
+  <si>
+    <t>纸塑袋：件数*5.5＋标准包材费用（不超过16.5元）</t>
+  </si>
+  <si>
+    <t>无纺布：16.5元</t>
+  </si>
+  <si>
+    <t>件数*5.5</t>
+  </si>
+  <si>
     <t>黑龙江省医院（香坊院区）</t>
   </si>
   <si>
-    <t>器械包-多少件（用120无纺布包装）</t>
-  </si>
-  <si>
-    <t>环氧乙烷组件-1包（医院自行打包）</t>
-  </si>
-  <si>
-    <t>固定30元</t>
-  </si>
-  <si>
-    <t>玻切包（自行打包）/W9050</t>
-  </si>
-  <si>
-    <t>固定35元</t>
-  </si>
-  <si>
-    <t>过氧化氢组件-1包</t>
-  </si>
-  <si>
-    <t>哈尔滨工业大学医院</t>
-  </si>
-  <si>
-    <r>
-      <t>包名称带“针架1</t>
-    </r>
-    <r>
-      <rPr>
+    <t>器械包-多少件/W12050</t>
+  </si>
+  <si>
+    <r>
+      <t>件数*5.5＋5元(只有</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="14"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>针多少</t>
+      <t>放疗科</t>
     </r>
     <r>
       <rPr>
@@ -1813,6 +1814,62 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>环氧乙烷组件-1包（医院自行打包）</t>
+  </si>
+  <si>
+    <t>固定30元</t>
+  </si>
+  <si>
+    <t>玻切包（自行打包）/W9050</t>
+  </si>
+  <si>
+    <t>固定35元</t>
+  </si>
+  <si>
+    <t>过氧化氢组件-1包</t>
+  </si>
+  <si>
+    <t>硬质容器盒-1</t>
+  </si>
+  <si>
+    <t>固定16.5元</t>
+  </si>
+  <si>
+    <t>哈尔滨工业大学医院</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>包名称带“针架1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>针多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>”</t>
     </r>
   </si>
@@ -1829,15 +1886,51 @@
     <t>固定77元</t>
   </si>
   <si>
+    <t>五常市人民医院</t>
+  </si>
+  <si>
+    <t>包名称带“骨元针”</t>
+  </si>
+  <si>
+    <t>包内件数/5（结果不是整数的都进一位）*5.5＋标准包材价格</t>
+  </si>
+  <si>
+    <t>黑龙江菁华上德生殖妇产医院</t>
+  </si>
+  <si>
+    <t>哈尔滨红十字医院</t>
+  </si>
+  <si>
+    <t>一件一包，和包名称无关</t>
+  </si>
+  <si>
+    <t>固定22元</t>
+  </si>
+  <si>
+    <t>单包装（EO）</t>
+  </si>
+  <si>
+    <t>针盒-1/W6050</t>
+  </si>
+  <si>
+    <t>哈尔滨市第二医院</t>
+  </si>
+  <si>
+    <t>分娩-消毒巾/Z3044</t>
+  </si>
+  <si>
+    <t>敷料包（纸塑袋）</t>
+  </si>
+  <si>
+    <t>包名称带“市二院外来”</t>
+  </si>
+  <si>
     <t>序号</t>
   </si>
   <si>
     <t>包名称带“克氏针”</t>
   </si>
   <si>
-    <t>包内件数/5（结果不是整数的都进一位）*5.5＋标准包材价格</t>
-  </si>
-  <si>
     <t>包名称带“银质针”</t>
   </si>
   <si>
@@ -1877,16 +1970,28 @@
     <t>通用（特殊的我单独标注）</t>
   </si>
   <si>
-    <t>敷料包（纸塑袋）</t>
-  </si>
-  <si>
     <t>纸塑袋宽＜20CM固定收费2.5元</t>
   </si>
   <si>
     <t>纸塑袋宽度≥20CM固定收费4元</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>通用外来器械收费</t>
+  </si>
+  <si>
+    <t>骨科租赁器械包-不带植入物</t>
+  </si>
+  <si>
+    <t>包内所有器械件数（包括篮筐）*5.5元</t>
+  </si>
+  <si>
+    <t>一套外来器械，整体有带植入物的，再+150元(市二院，市五院，骨伤科除外)</t>
+  </si>
+  <si>
+    <t>骨科租赁器械包-带植入物</t>
+  </si>
+  <si>
+    <t>[包内所有器械件数（包括篮筐）-（植入物-钉）件数]*5.5+50元</t>
   </si>
   <si>
     <t>低温过氧化氢和环氧乙烷灭菌通用收费</t>
@@ -2080,7 +2185,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-10804]0.000;\(0.000\)"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2118,16 +2223,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2180,6 +2285,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2547,7 +2658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2727,6 +2838,19 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2847,138 +2971,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="18">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="19">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="18">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="20">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="21">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3009,262 +3133,292 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3579,3210 +3733,3460 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="29" customWidth="1"/>
-    <col min="2" max="2" width="48" style="29" customWidth="1"/>
-    <col min="3" max="3" width="12" style="29" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="31" customWidth="1"/>
+    <col min="2" max="2" width="48" style="31" customWidth="1"/>
+    <col min="3" max="3" width="12" style="31" customWidth="1"/>
     <col min="4" max="4" width="44.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="25.8916666666667" style="10" customWidth="1"/>
-    <col min="6" max="6" width="17.3833333333333" style="29" customWidth="1"/>
+    <col min="5" max="5" width="25.8916666666667" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17.3833333333333" style="31" customWidth="1"/>
     <col min="7" max="7" width="100.333333333333" style="9" customWidth="1"/>
     <col min="8" max="8" width="57.1333333333333" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:8">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
-      <c r="A2" s="14">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="33"/>
+      <c r="G2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:8">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="33"/>
+      <c r="G3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:8">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="33"/>
+      <c r="G4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="32">
+      <c r="A5" s="34">
         <v>2</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="37" t="s">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="31" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="42"/>
+      <c r="H8" s="44"/>
     </row>
     <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="31" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="33"/>
+      <c r="G9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="15"/>
+      <c r="H9" s="16"/>
     </row>
     <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="31" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="15" t="s">
+      <c r="F10" s="33"/>
+      <c r="G10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="15"/>
+      <c r="H10" s="16"/>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>3</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="31" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="43"/>
+      <c r="H12" s="45"/>
     </row>
     <row r="13" customHeight="1" spans="1:8">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="43"/>
+      <c r="H13" s="45"/>
     </row>
     <row r="14" customHeight="1" spans="1:8">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="31" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="43"/>
+      <c r="H14" s="45"/>
     </row>
     <row r="15" customHeight="1" spans="1:8">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="43"/>
+      <c r="H15" s="45"/>
     </row>
     <row r="16" customHeight="1" spans="1:8">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="31" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="43"/>
+      <c r="H16" s="45"/>
     </row>
     <row r="17" customHeight="1" spans="1:8">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="14" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="43"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" customHeight="1" spans="1:8">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="31" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="43"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" customHeight="1" spans="1:8">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>4</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="43"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" customHeight="1" spans="1:8">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="31" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="43"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" customHeight="1" spans="1:8">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="43"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" customHeight="1" spans="1:8">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="31" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="43"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" customHeight="1" spans="1:8">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="14" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="43"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" customHeight="1" spans="1:8">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="31" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="43"/>
-    </row>
-    <row r="25" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45" t="s">
+      <c r="H24" s="45"/>
+    </row>
+    <row r="25" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="49"/>
-    </row>
-    <row r="26" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="47" t="s">
+      <c r="H25" s="51"/>
+    </row>
+    <row r="26" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="52"/>
+      <c r="H26" s="54"/>
     </row>
     <row r="27" customHeight="1" spans="1:8">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>5</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="15"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" customHeight="1" spans="1:8">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="31" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="15"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" customHeight="1" spans="1:8">
-      <c r="A29" s="14">
+      <c r="A29" s="15">
         <v>6</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H29" s="15"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" customHeight="1" spans="1:8">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="31" t="s">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="15"/>
+      <c r="H30" s="16"/>
     </row>
     <row r="31" customHeight="1" spans="1:8">
-      <c r="A31" s="31">
+      <c r="A31" s="33">
         <v>7</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="15" t="s">
+      <c r="F31" s="33"/>
+      <c r="G31" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H31" s="15"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" customHeight="1" spans="1:8">
-      <c r="A32" s="18">
+      <c r="A32" s="19">
         <v>8</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="15" t="s">
+      <c r="F32" s="33"/>
+      <c r="G32" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="15"/>
+      <c r="H32" s="16"/>
     </row>
     <row r="33" customHeight="1" spans="1:8">
-      <c r="A33" s="14">
+      <c r="A33" s="15">
         <v>9</v>
       </c>
-      <c r="B33" s="53" t="s">
+      <c r="B33" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="15" t="s">
+      <c r="F33" s="33"/>
+      <c r="G33" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="16" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:8">
-      <c r="A34" s="32"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="15" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="33"/>
+      <c r="G34" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="15"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" customHeight="1" spans="1:8">
-      <c r="A35" s="32"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="15" t="s">
+      <c r="A35" s="34"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="15" t="s">
+      <c r="F35" s="33"/>
+      <c r="G35" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="H35" s="15"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" customHeight="1" spans="1:8">
-      <c r="A36" s="14">
+      <c r="A36" s="15">
         <v>10</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="15"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" customHeight="1" spans="1:8">
-      <c r="A37" s="32"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="22" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="15"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" ht="38" customHeight="1" spans="1:8">
-      <c r="A38" s="55">
+      <c r="A38" s="57">
         <v>11</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H38" s="15"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" ht="41" customHeight="1" spans="1:8">
-      <c r="A39" s="58"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="14" t="s">
+      <c r="A39" s="60"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H39" s="15"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8">
-      <c r="A40" s="58"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="31" t="s">
+      <c r="A40" s="60"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="15"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8">
-      <c r="A41" s="58"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="31" t="s">
+      <c r="A41" s="60"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H41" s="15"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8">
-      <c r="A42" s="58"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="31" t="s">
+      <c r="A42" s="60"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="31" t="s">
+      <c r="F42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H42" s="15"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8">
-      <c r="A43" s="58"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="31" t="s">
+      <c r="A43" s="60"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="15"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8">
-      <c r="A44" s="58"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="31" t="s">
+      <c r="A44" s="60"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F44" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H44" s="15"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8">
-      <c r="A45" s="58"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="31" t="s">
+      <c r="A45" s="60"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="15"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8">
-      <c r="A46" s="58"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="31" t="s">
+      <c r="A46" s="60"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="15"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8">
-      <c r="A47" s="58"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="31" t="s">
+      <c r="A47" s="60"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="15"/>
+      <c r="H47" s="16"/>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8">
-      <c r="A48" s="58"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="31" t="s">
+      <c r="A48" s="60"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F48" s="31" t="s">
+      <c r="F48" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H48" s="15"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8">
-      <c r="A49" s="58"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="31" t="s">
+      <c r="A49" s="60"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="15"/>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8">
-      <c r="A50" s="58"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="31" t="s">
+      <c r="A50" s="60"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="15" t="s">
+      <c r="G50" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H50" s="15"/>
+      <c r="H50" s="16"/>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8">
-      <c r="A51" s="58"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="31" t="s">
+      <c r="A51" s="60"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G51" s="15" t="s">
+      <c r="G51" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="15"/>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8">
-      <c r="A52" s="58"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="31" t="s">
+      <c r="A52" s="60"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F52" s="31" t="s">
+      <c r="F52" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="G52" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H52" s="15"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8">
-      <c r="A53" s="58"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="31" t="s">
+      <c r="A53" s="60"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H53" s="15"/>
+      <c r="H53" s="16"/>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8">
-      <c r="A54" s="58"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="61" t="s">
+      <c r="A54" s="60"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="62" t="s">
+      <c r="D54" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="E54" s="63" t="s">
+      <c r="E54" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="F54" s="64"/>
-      <c r="G54" s="64" t="s">
+      <c r="F54" s="63"/>
+      <c r="G54" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="15"/>
+      <c r="H54" s="16"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8">
-      <c r="A55" s="58"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="61" t="s">
+      <c r="A55" s="60"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="62" t="s">
+      <c r="D55" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="F55" s="61" t="s">
+      <c r="F55" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="H55" s="15"/>
+      <c r="H55" s="16"/>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8">
-      <c r="A56" s="58"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="65"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="61" t="s">
+      <c r="A56" s="60"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G56" s="64" t="s">
+      <c r="G56" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="15"/>
+      <c r="H56" s="16"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8">
-      <c r="A57" s="58"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="66" t="s">
+      <c r="A57" s="60"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="62" t="s">
+      <c r="D57" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="62" t="s">
+      <c r="E57" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="F57" s="61" t="s">
+      <c r="F57" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="64" t="s">
+      <c r="G57" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="H57" s="15"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8">
-      <c r="A58" s="58"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="61" t="s">
+      <c r="A58" s="60"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G58" s="64" t="s">
+      <c r="G58" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="H58" s="15"/>
+      <c r="H58" s="16"/>
     </row>
     <row r="59" ht="39" customHeight="1" spans="1:8">
-      <c r="A59" s="58"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="67" t="s">
+      <c r="A59" s="60"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="E59" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F59" s="31" t="s">
+      <c r="F59" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="H59" s="15"/>
+      <c r="H59" s="16"/>
     </row>
     <row r="60" ht="30" customHeight="1" spans="1:8">
-      <c r="A60" s="58"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="14" t="s">
+      <c r="A60" s="60"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="G60" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H60" s="15"/>
-    </row>
-    <row r="61" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A61" s="69"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="71" t="s">
+      <c r="H60" s="16"/>
+    </row>
+    <row r="61" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A61" s="71"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="46" t="s">
+      <c r="D61" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="E61" s="72" t="s">
+      <c r="E61" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="F61" s="47"/>
-      <c r="G61" s="48" t="s">
+      <c r="F61" s="49"/>
+      <c r="G61" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H61" s="72">
+      <c r="H61" s="74">
         <v>121476</v>
       </c>
     </row>
-    <row r="62" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A62" s="69"/>
-      <c r="B62" s="70"/>
-      <c r="C62" s="71" t="s">
+    <row r="62" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A62" s="71"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="D62" s="72" t="s">
+      <c r="D62" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="E62" s="72" t="s">
+      <c r="E62" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="F62" s="50"/>
-      <c r="G62" s="48" t="s">
+      <c r="F62" s="52"/>
+      <c r="G62" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H62" s="72" t="s">
+      <c r="H62" s="74" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="63" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A63" s="69"/>
-      <c r="B63" s="70"/>
-      <c r="C63" s="71" t="s">
+    <row r="63" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A63" s="71"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="72" t="s">
+      <c r="D63" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="E63" s="72" t="s">
+      <c r="E63" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="F63" s="50"/>
-      <c r="G63" s="48" t="s">
+      <c r="F63" s="52"/>
+      <c r="G63" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H63" s="72" t="s">
+      <c r="H63" s="74" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="64" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A64" s="69"/>
-      <c r="B64" s="70"/>
-      <c r="C64" s="71" t="s">
+    <row r="64" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A64" s="71"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="72" t="s">
+      <c r="D64" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="E64" s="72" t="s">
+      <c r="E64" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="F64" s="50"/>
-      <c r="G64" s="48" t="s">
+      <c r="F64" s="52"/>
+      <c r="G64" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H64" s="72" t="s">
+      <c r="H64" s="74" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="65" s="28" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A65" s="69"/>
-      <c r="B65" s="73"/>
-      <c r="C65" s="74" t="s">
+    <row r="65" s="30" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A65" s="71"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="D65" s="72" t="s">
+      <c r="D65" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="E65" s="72" t="s">
+      <c r="E65" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="F65" s="50"/>
-      <c r="G65" s="48" t="s">
+      <c r="F65" s="52"/>
+      <c r="G65" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="H65" s="72" t="s">
+      <c r="H65" s="74" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:8">
-      <c r="A66" s="14">
+      <c r="A66" s="15">
         <v>12</v>
       </c>
-      <c r="B66" s="75" t="s">
+      <c r="B66" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="E66" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F66" s="31" t="s">
+      <c r="F66" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="G66" s="15" t="s">
+      <c r="G66" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H66" s="15"/>
+      <c r="H66" s="16"/>
     </row>
     <row r="67" customHeight="1" spans="1:8">
-      <c r="A67" s="18"/>
-      <c r="B67" s="76"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="31" t="s">
+      <c r="A67" s="19"/>
+      <c r="B67" s="78"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G67" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="H67" s="15"/>
+      <c r="H67" s="16"/>
     </row>
     <row r="68" customHeight="1" spans="1:8">
-      <c r="A68" s="14">
+      <c r="A68" s="15">
         <v>13</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="77" t="s">
+      <c r="D68" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F68" s="31"/>
-      <c r="G68" s="78">
+      <c r="F68" s="33"/>
+      <c r="G68" s="80">
         <v>16.5</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="14" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:8">
-      <c r="A69" s="32"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="79" t="s">
+      <c r="A69" s="34"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F69" s="31"/>
-      <c r="G69" s="80">
+      <c r="F69" s="33"/>
+      <c r="G69" s="82">
         <v>16.5</v>
       </c>
-      <c r="H69" s="20"/>
+      <c r="H69" s="21"/>
     </row>
     <row r="70" customHeight="1" spans="1:8">
-      <c r="A70" s="32"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="79" t="s">
+      <c r="A70" s="34"/>
+      <c r="B70" s="34"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="80">
+      <c r="F70" s="33"/>
+      <c r="G70" s="82">
         <v>16.5</v>
       </c>
-      <c r="H70" s="20"/>
+      <c r="H70" s="21"/>
     </row>
     <row r="71" customHeight="1" spans="1:8">
-      <c r="A71" s="32"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="79" t="s">
+      <c r="A71" s="34"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F71" s="31"/>
-      <c r="G71" s="80">
+      <c r="F71" s="33"/>
+      <c r="G71" s="82">
         <v>16.5</v>
       </c>
-      <c r="H71" s="20"/>
+      <c r="H71" s="21"/>
     </row>
     <row r="72" customHeight="1" spans="1:8">
-      <c r="A72" s="32"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="79" t="s">
+      <c r="A72" s="34"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="81" t="s">
         <v>126</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F72" s="31"/>
-      <c r="G72" s="80">
+      <c r="F72" s="33"/>
+      <c r="G72" s="82">
         <v>16.5</v>
       </c>
-      <c r="H72" s="20"/>
+      <c r="H72" s="21"/>
     </row>
     <row r="73" customHeight="1" spans="1:8">
-      <c r="A73" s="32"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="77" t="s">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F73" s="31"/>
-      <c r="G73" s="78">
+      <c r="F73" s="33"/>
+      <c r="G73" s="80">
         <v>16.5</v>
       </c>
-      <c r="H73" s="20"/>
+      <c r="H73" s="21"/>
     </row>
     <row r="74" customHeight="1" spans="1:8">
-      <c r="A74" s="32"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="79" t="s">
+      <c r="A74" s="34"/>
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="80">
+      <c r="F74" s="33"/>
+      <c r="G74" s="82">
         <v>16.5</v>
       </c>
-      <c r="H74" s="20"/>
+      <c r="H74" s="21"/>
     </row>
     <row r="75" customHeight="1" spans="1:8">
-      <c r="A75" s="32"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="79" t="s">
+      <c r="A75" s="34"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F75" s="31"/>
-      <c r="G75" s="80">
+      <c r="F75" s="33"/>
+      <c r="G75" s="82">
         <v>22</v>
       </c>
-      <c r="H75" s="20"/>
+      <c r="H75" s="21"/>
     </row>
     <row r="76" customHeight="1" spans="1:8">
-      <c r="A76" s="32"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="79" t="s">
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="34"/>
+      <c r="D76" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F76" s="31"/>
-      <c r="G76" s="80">
+      <c r="F76" s="33"/>
+      <c r="G76" s="82">
         <v>22</v>
       </c>
-      <c r="H76" s="20"/>
+      <c r="H76" s="21"/>
     </row>
     <row r="77" customHeight="1" spans="1:8">
-      <c r="A77" s="32"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="79" t="s">
+      <c r="A77" s="34"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F77" s="31"/>
-      <c r="G77" s="80">
+      <c r="F77" s="33"/>
+      <c r="G77" s="82">
         <v>44</v>
       </c>
-      <c r="H77" s="20"/>
+      <c r="H77" s="21"/>
     </row>
     <row r="78" customHeight="1" spans="1:8">
-      <c r="A78" s="32"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="79" t="s">
+      <c r="A78" s="34"/>
+      <c r="B78" s="34"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F78" s="31"/>
-      <c r="G78" s="80">
+      <c r="F78" s="33"/>
+      <c r="G78" s="82">
         <v>44</v>
       </c>
-      <c r="H78" s="20"/>
+      <c r="H78" s="21"/>
     </row>
     <row r="79" customHeight="1" spans="1:8">
-      <c r="A79" s="32"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="81" t="s">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="83" t="s">
         <v>133</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F79" s="31"/>
-      <c r="G79" s="78">
+      <c r="F79" s="33"/>
+      <c r="G79" s="80">
         <v>44</v>
       </c>
-      <c r="H79" s="20"/>
+      <c r="H79" s="21"/>
     </row>
     <row r="80" customHeight="1" spans="1:8">
-      <c r="A80" s="32"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="79" t="s">
+      <c r="A80" s="34"/>
+      <c r="B80" s="34"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F80" s="31"/>
-      <c r="G80" s="80">
+      <c r="F80" s="33"/>
+      <c r="G80" s="82">
         <v>44</v>
       </c>
-      <c r="H80" s="20"/>
+      <c r="H80" s="21"/>
     </row>
     <row r="81" customHeight="1" spans="1:8">
-      <c r="A81" s="18"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="79" t="s">
+      <c r="A81" s="19"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F81" s="31"/>
-      <c r="G81" s="80">
+      <c r="F81" s="33"/>
+      <c r="G81" s="82">
         <v>44</v>
       </c>
-      <c r="H81" s="17"/>
+      <c r="H81" s="18"/>
     </row>
     <row r="82" customHeight="1" spans="1:8">
-      <c r="A82" s="14">
+      <c r="A82" s="15">
         <v>14</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E82" s="13" t="s">
+      <c r="E82" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G82" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H82" s="13" t="s">
+      <c r="H82" s="14" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:8">
-      <c r="A83" s="32"/>
-      <c r="B83" s="32"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="31" t="s">
+      <c r="A83" s="34"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G83" s="15" t="s">
+      <c r="G83" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H83" s="17"/>
+      <c r="H83" s="18"/>
     </row>
     <row r="84" customHeight="1" spans="1:8">
-      <c r="A84" s="32"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="14" t="s">
+      <c r="A84" s="34"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="E84" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F84" s="31" t="s">
+      <c r="F84" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G84" s="15" t="s">
+      <c r="G84" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H84" s="15"/>
+      <c r="H84" s="16"/>
     </row>
     <row r="85" customHeight="1" spans="1:8">
-      <c r="A85" s="18"/>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="31" t="s">
+      <c r="A85" s="19"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G85" s="15" t="s">
+      <c r="G85" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H85" s="15"/>
+      <c r="H85" s="16"/>
     </row>
     <row r="86" customHeight="1" spans="1:8">
-      <c r="A86" s="14">
+      <c r="A86" s="15">
         <v>15</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="F86" s="31" t="s">
+      <c r="F86" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G86" s="15" t="s">
+      <c r="G86" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="H86" s="15"/>
+      <c r="H86" s="16"/>
     </row>
     <row r="87" customHeight="1" spans="1:8">
-      <c r="A87" s="18"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="22"/>
-      <c r="F87" s="31" t="s">
+      <c r="A87" s="19"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G87" s="15" t="s">
+      <c r="G87" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="H87" s="15"/>
+      <c r="H87" s="16"/>
     </row>
     <row r="88" customHeight="1" spans="1:8">
-      <c r="A88" s="14">
+      <c r="A88" s="15">
         <v>16</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D88" s="82" t="s">
+      <c r="D88" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="E88" s="20" t="s">
+      <c r="E88" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="F88" s="31"/>
-      <c r="G88" s="57" t="s">
+      <c r="F88" s="33"/>
+      <c r="G88" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="H88" s="82">
+      <c r="H88" s="84">
         <v>20008068</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:8">
-      <c r="A89" s="32"/>
-      <c r="B89" s="32"/>
-      <c r="C89" s="32"/>
-      <c r="D89" s="82" t="s">
+      <c r="A89" s="34"/>
+      <c r="B89" s="34"/>
+      <c r="C89" s="34"/>
+      <c r="D89" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="83"/>
-      <c r="H89" s="82">
+      <c r="E89" s="21"/>
+      <c r="F89" s="33"/>
+      <c r="G89" s="85"/>
+      <c r="H89" s="84">
         <v>20008067</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:8">
-      <c r="A90" s="32"/>
-      <c r="B90" s="32"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="84" t="s">
+      <c r="A90" s="34"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="86" t="s">
         <v>148</v>
       </c>
-      <c r="E90" s="20"/>
-      <c r="F90" s="31"/>
-      <c r="G90" s="83"/>
-      <c r="H90" s="82">
+      <c r="E90" s="21"/>
+      <c r="F90" s="33"/>
+      <c r="G90" s="85"/>
+      <c r="H90" s="84">
         <v>20008066</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:8">
-      <c r="A91" s="32"/>
-      <c r="B91" s="32"/>
-      <c r="C91" s="32"/>
-      <c r="D91" s="84" t="s">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+      <c r="D91" s="86" t="s">
         <v>149</v>
       </c>
-      <c r="E91" s="20"/>
-      <c r="F91" s="31"/>
-      <c r="G91" s="83"/>
-      <c r="H91" s="82">
+      <c r="E91" s="21"/>
+      <c r="F91" s="33"/>
+      <c r="G91" s="85"/>
+      <c r="H91" s="84">
         <v>20348951</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:8">
-      <c r="A92" s="18"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="84" t="s">
+      <c r="A92" s="19"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="86" t="s">
         <v>150</v>
       </c>
-      <c r="E92" s="17"/>
-      <c r="F92" s="31"/>
-      <c r="G92" s="85"/>
-      <c r="H92" s="82">
+      <c r="E92" s="18"/>
+      <c r="F92" s="33"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="84">
         <v>20009182</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:8">
-      <c r="A93" s="14">
+      <c r="A93" s="15">
         <v>17</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C93" s="31" t="s">
+      <c r="C93" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F93" s="31"/>
-      <c r="G93" s="15" t="s">
+      <c r="F93" s="33"/>
+      <c r="G93" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="H93" s="15"/>
+      <c r="H93" s="16"/>
     </row>
     <row r="94" customHeight="1" spans="1:8">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="31" t="s">
+      <c r="A94" s="19"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D94" s="15" t="s">
+      <c r="D94" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E94" s="22" t="s">
+      <c r="E94" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F94" s="31"/>
-      <c r="G94" s="15" t="s">
+      <c r="F94" s="33"/>
+      <c r="G94" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="H94" s="15"/>
+      <c r="H94" s="16"/>
     </row>
     <row r="95" customHeight="1" spans="1:8">
-      <c r="A95" s="31">
+      <c r="A95" s="33">
         <v>18</v>
       </c>
-      <c r="B95" s="31" t="s">
+      <c r="B95" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="C95" s="31" t="s">
+      <c r="C95" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="31" t="s">
+      <c r="F95" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G95" s="15" t="s">
+      <c r="G95" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="H95" s="15"/>
+      <c r="H95" s="16"/>
     </row>
     <row r="96" customHeight="1" spans="1:8">
-      <c r="A96" s="14">
+      <c r="A96" s="15">
         <v>19</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D96" s="57" t="s">
+      <c r="D96" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="E96" s="13" t="s">
+      <c r="E96" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F96" s="14" t="s">
+      <c r="F96" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G96" s="13" t="s">
+      <c r="G96" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H96" s="15"/>
+      <c r="H96" s="16"/>
     </row>
     <row r="97" customHeight="1" spans="1:8">
-      <c r="A97" s="18"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="60"/>
-      <c r="E97" s="20"/>
-      <c r="F97" s="14" t="s">
+      <c r="A97" s="19"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="62"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G97" s="13" t="s">
+      <c r="G97" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H97" s="15"/>
+      <c r="H97" s="16"/>
     </row>
     <row r="98" customHeight="1" spans="1:8">
-      <c r="A98" s="14">
+      <c r="A98" s="15">
         <v>20</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C98" s="31" t="s">
+      <c r="C98" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D98" s="15" t="s">
+      <c r="D98" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E98" s="22" t="s">
+      <c r="E98" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F98" s="31"/>
-      <c r="G98" s="15" t="s">
+      <c r="F98" s="33"/>
+      <c r="G98" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H98" s="15" t="s">
+      <c r="H98" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:8">
-      <c r="A99" s="32"/>
-      <c r="B99" s="32"/>
-      <c r="C99" s="31" t="s">
+      <c r="A99" s="34"/>
+      <c r="B99" s="34"/>
+      <c r="C99" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="15" t="s">
+      <c r="D99" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E99" s="22" t="s">
+      <c r="E99" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F99" s="31"/>
-      <c r="G99" s="15" t="s">
+      <c r="F99" s="33"/>
+      <c r="G99" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H99" s="15" t="s">
+      <c r="H99" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:8">
-      <c r="A100" s="32"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="31" t="s">
+      <c r="A100" s="34"/>
+      <c r="B100" s="34"/>
+      <c r="C100" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D100" s="34" t="s">
+      <c r="D100" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="E100" s="22" t="s">
+      <c r="E100" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F100" s="31"/>
-      <c r="G100" s="15" t="s">
+      <c r="F100" s="33"/>
+      <c r="G100" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H100" s="15" t="s">
+      <c r="H100" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:8">
-      <c r="A101" s="32"/>
-      <c r="B101" s="32"/>
-      <c r="C101" s="14" t="s">
+      <c r="A101" s="34"/>
+      <c r="B101" s="34"/>
+      <c r="C101" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D101" s="57" t="s">
+      <c r="D101" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E101" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F101" s="14" t="s">
+      <c r="F101" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H101" s="15"/>
+      <c r="H101" s="16"/>
     </row>
     <row r="102" customHeight="1" spans="1:8">
-      <c r="A102" s="18"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="60"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="14" t="s">
+      <c r="A102" s="19"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="62"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G102" s="13" t="s">
+      <c r="G102" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H102" s="15"/>
+      <c r="H102" s="16"/>
     </row>
     <row r="103" customHeight="1" spans="1:8">
-      <c r="A103" s="14">
+      <c r="A103" s="15">
         <v>21</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E103" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F103" s="31" t="s">
+      <c r="F103" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G103" s="15" t="s">
+      <c r="G103" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="H103" s="15"/>
+      <c r="H103" s="16"/>
     </row>
     <row r="104" customHeight="1" spans="1:8">
-      <c r="A104" s="18"/>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="14" t="s">
+      <c r="A104" s="19"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="19"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G104" s="20" t="s">
+      <c r="G104" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H104" s="15"/>
+      <c r="H104" s="16"/>
     </row>
     <row r="105" customHeight="1" spans="1:8">
-      <c r="A105" s="14">
+      <c r="A105" s="15">
         <v>22</v>
       </c>
-      <c r="B105" s="41" t="s">
+      <c r="B105" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="C105" s="31" t="s">
+      <c r="C105" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E105" s="22" t="s">
+      <c r="E105" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F105" s="31"/>
-      <c r="G105" s="15" t="s">
+      <c r="F105" s="33"/>
+      <c r="G105" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H105" s="13" t="s">
+      <c r="H105" s="14" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:8">
-      <c r="A106" s="32"/>
-      <c r="B106" s="43"/>
-      <c r="C106" s="31" t="s">
+      <c r="A106" s="34"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="15" t="s">
+      <c r="D106" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F106" s="31"/>
-      <c r="G106" s="15" t="s">
+      <c r="F106" s="33"/>
+      <c r="G106" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H106" s="20"/>
+      <c r="H106" s="21"/>
     </row>
     <row r="107" customHeight="1" spans="1:8">
-      <c r="A107" s="32"/>
-      <c r="B107" s="43"/>
-      <c r="C107" s="31" t="s">
+      <c r="A107" s="34"/>
+      <c r="B107" s="45"/>
+      <c r="C107" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="E107" s="22" t="s">
+      <c r="E107" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F107" s="31"/>
-      <c r="G107" s="15" t="s">
+      <c r="F107" s="33"/>
+      <c r="G107" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H107" s="20"/>
+      <c r="H107" s="21"/>
     </row>
     <row r="108" customHeight="1" spans="1:8">
-      <c r="A108" s="32"/>
-      <c r="B108" s="43"/>
-      <c r="C108" s="31" t="s">
+      <c r="A108" s="34"/>
+      <c r="B108" s="45"/>
+      <c r="C108" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D108" s="15" t="s">
+      <c r="D108" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E108" s="22" t="s">
+      <c r="E108" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F108" s="31"/>
-      <c r="G108" s="15" t="s">
+      <c r="F108" s="33"/>
+      <c r="G108" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H108" s="20"/>
+      <c r="H108" s="21"/>
     </row>
     <row r="109" customHeight="1" spans="1:8">
-      <c r="A109" s="32"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="31" t="s">
+      <c r="A109" s="34"/>
+      <c r="B109" s="45"/>
+      <c r="C109" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="D109" s="15" t="s">
+      <c r="D109" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="E109" s="22" t="s">
+      <c r="E109" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F109" s="31"/>
-      <c r="G109" s="15" t="s">
+      <c r="F109" s="33"/>
+      <c r="G109" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H109" s="20"/>
+      <c r="H109" s="21"/>
     </row>
     <row r="110" customHeight="1" spans="1:8">
-      <c r="A110" s="32"/>
-      <c r="B110" s="43"/>
-      <c r="C110" s="31" t="s">
+      <c r="A110" s="34"/>
+      <c r="B110" s="45"/>
+      <c r="C110" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D110" s="15" t="s">
+      <c r="D110" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="E110" s="22" t="s">
+      <c r="E110" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F110" s="31"/>
-      <c r="G110" s="15" t="s">
+      <c r="F110" s="33"/>
+      <c r="G110" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H110" s="20"/>
+      <c r="H110" s="21"/>
     </row>
     <row r="111" customHeight="1" spans="1:8">
-      <c r="A111" s="32"/>
-      <c r="B111" s="43"/>
-      <c r="C111" s="31" t="s">
+      <c r="A111" s="34"/>
+      <c r="B111" s="45"/>
+      <c r="C111" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D111" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E111" s="22" t="s">
+      <c r="E111" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F111" s="31"/>
-      <c r="G111" s="15" t="s">
+      <c r="F111" s="33"/>
+      <c r="G111" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="H111" s="20"/>
+      <c r="H111" s="21"/>
     </row>
     <row r="112" customHeight="1" spans="1:8">
-      <c r="A112" s="18"/>
-      <c r="B112" s="42"/>
-      <c r="C112" s="31" t="s">
+      <c r="A112" s="19"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="D112" s="15" t="s">
+      <c r="D112" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="E112" s="22" t="s">
+      <c r="E112" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F112" s="31"/>
-      <c r="G112" s="15" t="s">
+      <c r="F112" s="33"/>
+      <c r="G112" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="H112" s="17"/>
+      <c r="H112" s="18"/>
     </row>
     <row r="113" customHeight="1" spans="1:8">
-      <c r="A113" s="14">
+      <c r="A113" s="15">
         <v>23</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D113" s="14" t="s">
+      <c r="D113" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E113" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="F113" s="31" t="s">
+      <c r="F113" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="G113" s="15" t="s">
+      <c r="G113" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="H113" s="15"/>
+      <c r="H113" s="16"/>
     </row>
     <row r="114" customHeight="1" spans="1:8">
-      <c r="A114" s="18"/>
-      <c r="B114" s="18"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="86"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="31" t="s">
+      <c r="A114" s="19"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="88"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="G114" s="15" t="s">
+      <c r="G114" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="H114" s="15"/>
+      <c r="H114" s="16"/>
     </row>
     <row r="115" customHeight="1" spans="1:8">
-      <c r="A115" s="14">
+      <c r="A115" s="15">
         <v>24</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C115" s="14" t="s">
+      <c r="C115" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D115" s="57" t="s">
+      <c r="D115" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="E115" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F115" s="14" t="s">
+      <c r="F115" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G115" s="13" t="s">
+      <c r="G115" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H115" s="15"/>
+      <c r="H115" s="16"/>
     </row>
     <row r="116" customHeight="1" spans="1:8">
-      <c r="A116" s="32"/>
-      <c r="B116" s="32"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="60"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="14" t="s">
+      <c r="A116" s="34"/>
+      <c r="B116" s="34"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="62"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G116" s="13" t="s">
+      <c r="G116" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H116" s="15"/>
+      <c r="H116" s="16"/>
     </row>
     <row r="117" customHeight="1" spans="1:8">
-      <c r="A117" s="18"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="14" t="s">
+      <c r="A117" s="19"/>
+      <c r="B117" s="19"/>
+      <c r="C117" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D117" s="57" t="s">
+      <c r="D117" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="E117" s="13" t="s">
+      <c r="E117" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F117" s="31"/>
-      <c r="G117" s="22" t="s">
+      <c r="F117" s="33"/>
+      <c r="G117" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="H117" s="15"/>
+      <c r="H117" s="16"/>
     </row>
     <row r="118" customHeight="1" spans="1:8">
-      <c r="A118" s="14">
+      <c r="A118" s="15">
         <v>25</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C118" s="14" t="s">
+      <c r="C118" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E118" s="13" t="s">
+      <c r="E118" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F118" s="31" t="s">
+      <c r="F118" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G118" s="15" t="s">
+      <c r="G118" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H118" s="15"/>
+      <c r="H118" s="16"/>
     </row>
     <row r="119" customHeight="1" spans="1:8">
-      <c r="A119" s="18"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="31" t="s">
+      <c r="A119" s="19"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G119" s="15" t="s">
+      <c r="G119" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H119" s="15"/>
+      <c r="H119" s="16"/>
     </row>
     <row r="120" customHeight="1" spans="1:8">
-      <c r="A120" s="14">
+      <c r="A120" s="15">
         <v>26</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C120" s="14" t="s">
+      <c r="C120" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E120" s="13" t="s">
+      <c r="E120" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F120" s="31" t="s">
+      <c r="F120" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G120" s="15" t="s">
+      <c r="G120" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H120" s="15"/>
+      <c r="H120" s="16"/>
     </row>
     <row r="121" customHeight="1" spans="1:8">
-      <c r="A121" s="18"/>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="31" t="s">
+      <c r="A121" s="19"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G121" s="15" t="s">
+      <c r="G121" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H121" s="15"/>
+      <c r="H121" s="16"/>
     </row>
     <row r="122" customHeight="1" spans="1:8">
-      <c r="A122" s="14">
+      <c r="A122" s="15">
         <v>27</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="E122" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F122" s="31" t="s">
+      <c r="F122" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G122" s="15" t="s">
+      <c r="G122" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H122" s="15"/>
+      <c r="H122" s="16"/>
     </row>
     <row r="123" customHeight="1" spans="1:8">
-      <c r="A123" s="18"/>
-      <c r="B123" s="18"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="17"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="31" t="s">
+      <c r="A123" s="19"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="19"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G123" s="15" t="s">
+      <c r="G123" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H123" s="15"/>
+      <c r="H123" s="16"/>
     </row>
     <row r="124" customHeight="1" spans="1:8">
-      <c r="A124" s="14">
+      <c r="A124" s="15">
         <v>28</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C124" s="31" t="s">
+      <c r="C124" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D124" s="87" t="s">
+      <c r="D124" s="89" t="s">
         <v>194</v>
       </c>
-      <c r="E124" s="22" t="s">
+      <c r="E124" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F124" s="31"/>
-      <c r="G124" s="15" t="s">
+      <c r="F124" s="33"/>
+      <c r="G124" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="H124" s="15"/>
+      <c r="H124" s="16"/>
     </row>
     <row r="125" customHeight="1" spans="1:8">
-      <c r="A125" s="18"/>
-      <c r="B125" s="18"/>
-      <c r="C125" s="31" t="s">
+      <c r="A125" s="19"/>
+      <c r="B125" s="19"/>
+      <c r="C125" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D125" s="88" t="s">
+      <c r="D125" s="90" t="s">
         <v>196</v>
       </c>
-      <c r="E125" s="22" t="s">
+      <c r="E125" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F125" s="31"/>
-      <c r="G125" s="15" t="s">
+      <c r="F125" s="33"/>
+      <c r="G125" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="H125" s="15"/>
+      <c r="H125" s="16"/>
     </row>
     <row r="126" customHeight="1" spans="1:8">
-      <c r="A126" s="14">
+      <c r="A126" s="15">
         <v>29</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E126" s="13" t="s">
+      <c r="E126" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F126" s="31" t="s">
+      <c r="F126" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G126" s="15" t="s">
+      <c r="G126" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="H126" s="15"/>
+      <c r="H126" s="16"/>
     </row>
     <row r="127" customHeight="1" spans="1:8">
-      <c r="A127" s="32"/>
-      <c r="B127" s="32"/>
-      <c r="C127" s="18"/>
-      <c r="D127" s="17"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="31" t="s">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="19"/>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="G127" s="15" t="s">
+      <c r="G127" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H127" s="15"/>
+      <c r="H127" s="16"/>
     </row>
     <row r="128" customHeight="1" spans="1:8">
-      <c r="A128" s="32"/>
-      <c r="B128" s="32"/>
-      <c r="C128" s="14" t="s">
+      <c r="A128" s="34"/>
+      <c r="B128" s="34"/>
+      <c r="C128" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D128" s="57" t="s">
+      <c r="D128" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="E128" s="13" t="s">
+      <c r="E128" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F128" s="14" t="s">
+      <c r="F128" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G128" s="13" t="s">
+      <c r="G128" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H128" s="15"/>
+      <c r="H128" s="16"/>
     </row>
     <row r="129" customHeight="1" spans="1:8">
-      <c r="A129" s="18"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="60"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="14" t="s">
+      <c r="A129" s="19"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="19"/>
+      <c r="D129" s="62"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G129" s="13" t="s">
+      <c r="G129" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H129" s="15"/>
+      <c r="H129" s="16"/>
     </row>
     <row r="130" customHeight="1" spans="1:8">
-      <c r="A130" s="14">
+      <c r="A130" s="15">
         <v>30</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="E130" s="13" t="s">
+      <c r="E130" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F130" s="31" t="s">
+      <c r="F130" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G130" s="15" t="s">
+      <c r="G130" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H130" s="15"/>
+      <c r="H130" s="16"/>
     </row>
     <row r="131" customHeight="1" spans="1:8">
-      <c r="A131" s="32"/>
-      <c r="B131" s="32"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="17"/>
-      <c r="E131" s="17"/>
-      <c r="F131" s="31" t="s">
+      <c r="A131" s="34"/>
+      <c r="B131" s="34"/>
+      <c r="C131" s="19"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G131" s="15" t="s">
+      <c r="G131" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H131" s="15"/>
+      <c r="H131" s="16"/>
     </row>
     <row r="132" customHeight="1" spans="1:8">
-      <c r="A132" s="32"/>
-      <c r="B132" s="32"/>
-      <c r="C132" s="14" t="s">
+      <c r="A132" s="34"/>
+      <c r="B132" s="34"/>
+      <c r="C132" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E132" s="13" t="s">
+      <c r="E132" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F132" s="31" t="s">
+      <c r="F132" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G132" s="15" t="s">
+      <c r="G132" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H132" s="15"/>
+      <c r="H132" s="16"/>
     </row>
     <row r="133" customHeight="1" spans="1:8">
-      <c r="A133" s="32"/>
-      <c r="B133" s="32"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="17"/>
-      <c r="E133" s="17"/>
-      <c r="F133" s="31" t="s">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="19"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G133" s="15" t="s">
+      <c r="G133" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H133" s="15"/>
+      <c r="H133" s="16"/>
     </row>
     <row r="134" customHeight="1" spans="1:8">
-      <c r="A134" s="32"/>
-      <c r="B134" s="32"/>
-      <c r="C134" s="31" t="s">
+      <c r="A134" s="34"/>
+      <c r="B134" s="34"/>
+      <c r="C134" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D134" s="57" t="s">
+      <c r="D134" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="E134" s="22" t="s">
+      <c r="E134" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="F134" s="31"/>
-      <c r="G134" s="15" t="s">
+      <c r="F134" s="33"/>
+      <c r="G134" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="H134" s="15"/>
+      <c r="H134" s="16"/>
     </row>
     <row r="135" customHeight="1" spans="1:8">
-      <c r="A135" s="18"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="31" t="s">
+      <c r="A135" s="19"/>
+      <c r="B135" s="19"/>
+      <c r="C135" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D135" s="89" t="s">
+      <c r="D135" s="91" t="s">
         <v>205</v>
       </c>
-      <c r="E135" s="22" t="s">
+      <c r="E135" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F135" s="31"/>
-      <c r="G135" s="15" t="s">
+      <c r="F135" s="33"/>
+      <c r="G135" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H135" s="15"/>
+      <c r="H135" s="16"/>
     </row>
     <row r="136" customHeight="1" spans="1:8">
-      <c r="A136" s="31">
+      <c r="A136" s="33">
         <v>31</v>
       </c>
-      <c r="B136" s="31" t="s">
+      <c r="B136" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C136" s="31" t="s">
+      <c r="C136" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D136" s="90" t="s">
+      <c r="D136" s="92" t="s">
         <v>208</v>
       </c>
-      <c r="E136" s="91" t="s">
+      <c r="E136" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="F136" s="92"/>
-      <c r="G136" s="15" t="s">
+      <c r="F136" s="94"/>
+      <c r="G136" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H136" s="15"/>
+      <c r="H136" s="16"/>
     </row>
     <row r="137" customHeight="1" spans="1:8">
-      <c r="A137" s="14">
+      <c r="A137" s="15">
         <v>32</v>
       </c>
-      <c r="B137" s="93" t="s">
+      <c r="B137" s="95" t="s">
         <v>211</v>
       </c>
-      <c r="C137" s="31" t="s">
+      <c r="C137" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D137" s="15" t="s">
+      <c r="D137" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E137" s="22" t="s">
+      <c r="E137" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F137" s="31"/>
-      <c r="G137" s="15" t="s">
+      <c r="F137" s="33"/>
+      <c r="G137" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H137" s="15"/>
+      <c r="H137" s="16"/>
     </row>
     <row r="138" customHeight="1" spans="1:8">
-      <c r="A138" s="32"/>
-      <c r="B138" s="32"/>
-      <c r="C138" s="31" t="s">
+      <c r="A138" s="34"/>
+      <c r="B138" s="34"/>
+      <c r="C138" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D138" s="33" t="s">
+      <c r="D138" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E138" s="22" t="s">
+      <c r="E138" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F138" s="31"/>
-      <c r="G138" s="15" t="s">
+      <c r="F138" s="33"/>
+      <c r="G138" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H138" s="15"/>
+      <c r="H138" s="16"/>
     </row>
     <row r="139" customHeight="1" spans="1:8">
-      <c r="A139" s="18"/>
-      <c r="B139" s="18"/>
-      <c r="C139" s="31" t="s">
+      <c r="A139" s="19"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D139" s="34" t="s">
+      <c r="D139" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E139" s="22" t="s">
+      <c r="E139" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F139" s="31"/>
-      <c r="G139" s="15" t="s">
+      <c r="F139" s="33"/>
+      <c r="G139" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H139" s="15"/>
+      <c r="H139" s="16"/>
     </row>
     <row r="140" customHeight="1" spans="1:8">
-      <c r="A140" s="14">
+      <c r="A140" s="15">
         <v>33</v>
       </c>
-      <c r="B140" s="14" t="s">
+      <c r="B140" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C140" s="31" t="s">
+      <c r="C140" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D140" s="87" t="s">
+      <c r="D140" s="89" t="s">
         <v>213</v>
       </c>
-      <c r="E140" s="22" t="s">
+      <c r="E140" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F140" s="31"/>
-      <c r="G140" s="15" t="s">
+      <c r="F140" s="33"/>
+      <c r="G140" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="H140" s="15"/>
+      <c r="H140" s="16"/>
     </row>
     <row r="141" customHeight="1" spans="1:8">
-      <c r="A141" s="32"/>
-      <c r="B141" s="32"/>
-      <c r="C141" s="14" t="s">
+      <c r="A141" s="34"/>
+      <c r="B141" s="34"/>
+      <c r="C141" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D141" s="57" t="s">
+      <c r="D141" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="E141" s="94" t="s">
+      <c r="E141" s="96" t="s">
         <v>217</v>
       </c>
-      <c r="F141" s="14" t="s">
+      <c r="F141" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G141" s="13" t="s">
+      <c r="G141" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H141" s="15"/>
+      <c r="H141" s="16"/>
     </row>
     <row r="142" customHeight="1" spans="1:8">
-      <c r="A142" s="32"/>
-      <c r="B142" s="32"/>
-      <c r="C142" s="18"/>
-      <c r="D142" s="60"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="14" t="s">
+      <c r="A142" s="34"/>
+      <c r="B142" s="34"/>
+      <c r="C142" s="19"/>
+      <c r="D142" s="62"/>
+      <c r="E142" s="18"/>
+      <c r="F142" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H142" s="15"/>
+      <c r="H142" s="16"/>
     </row>
     <row r="143" customHeight="1" spans="1:8">
-      <c r="A143" s="32"/>
-      <c r="B143" s="32"/>
-      <c r="C143" s="14" t="s">
+      <c r="A143" s="34"/>
+      <c r="B143" s="34"/>
+      <c r="C143" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D143" s="57" t="s">
+      <c r="D143" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="E143" s="13" t="s">
+      <c r="E143" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F143" s="14" t="s">
+      <c r="F143" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H143" s="15"/>
+      <c r="H143" s="16"/>
     </row>
     <row r="144" customHeight="1" spans="1:8">
-      <c r="A144" s="18"/>
-      <c r="B144" s="18"/>
-      <c r="C144" s="18"/>
-      <c r="D144" s="60"/>
-      <c r="E144" s="20"/>
-      <c r="F144" s="14" t="s">
+      <c r="A144" s="19"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="62"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G144" s="13" t="s">
+      <c r="G144" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H144" s="15"/>
+      <c r="H144" s="16"/>
     </row>
     <row r="145" customHeight="1" spans="1:8">
-      <c r="A145" s="14">
+      <c r="A145" s="15">
         <v>34</v>
       </c>
-      <c r="B145" s="14" t="s">
+      <c r="B145" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C145" s="35" t="s">
+      <c r="C145" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D145" s="36" t="s">
+      <c r="D145" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E145" s="36" t="s">
+      <c r="E145" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="F145" s="37" t="s">
+      <c r="F145" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G145" s="38" t="s">
+      <c r="G145" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="H145" s="15"/>
+      <c r="H145" s="16"/>
     </row>
     <row r="146" customHeight="1" spans="1:8">
-      <c r="A146" s="32"/>
-      <c r="B146" s="32"/>
-      <c r="C146" s="39"/>
-      <c r="D146" s="40"/>
-      <c r="E146" s="40"/>
-      <c r="F146" s="37" t="s">
+      <c r="A146" s="34"/>
+      <c r="B146" s="34"/>
+      <c r="C146" s="41"/>
+      <c r="D146" s="42"/>
+      <c r="E146" s="42"/>
+      <c r="F146" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="G146" s="38" t="s">
+      <c r="G146" s="40" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:8">
-      <c r="A147" s="18"/>
-      <c r="B147" s="18"/>
-      <c r="C147" s="31" t="s">
+      <c r="A147" s="34"/>
+      <c r="B147" s="34"/>
+      <c r="C147" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D147" s="57" t="s">
+      <c r="D147" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="E147" s="22" t="s">
+      <c r="E147" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F147" s="31" t="s">
+      <c r="F147" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="G147" s="15" t="s">
+      <c r="G147" s="16" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:8">
-      <c r="A148" s="14">
+      <c r="A148" s="34"/>
+      <c r="B148" s="34"/>
+      <c r="C148" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="E148" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="33"/>
+      <c r="G148" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:8">
+      <c r="A149" s="15">
         <v>35</v>
       </c>
-      <c r="B148" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="C148" s="31" t="s">
+      <c r="B149" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C149" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D148" s="89" t="s">
-        <v>226</v>
-      </c>
-      <c r="E148" s="22" t="s">
+      <c r="D149" s="91" t="s">
+        <v>227</v>
+      </c>
+      <c r="E149" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F148" s="31"/>
-      <c r="G148" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" spans="1:8">
-      <c r="A149" s="32"/>
-      <c r="B149" s="32"/>
-      <c r="C149" s="31" t="s">
+      <c r="F149" s="33"/>
+      <c r="G149" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:8">
+      <c r="A150" s="34"/>
+      <c r="B150" s="34"/>
+      <c r="C150" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D149" s="77" t="s">
+      <c r="D150" s="79" t="s">
+        <v>229</v>
+      </c>
+      <c r="E150" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="F150" s="33"/>
+      <c r="G150" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E149" s="22" t="s">
+    </row>
+    <row r="151" customHeight="1" spans="1:8">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D151" s="79" t="s">
+        <v>230</v>
+      </c>
+      <c r="E151" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="F149" s="31"/>
-      <c r="G149" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="1:8">
-      <c r="A150" s="32"/>
-      <c r="B150" s="32"/>
-      <c r="C150" s="31" t="s">
+      <c r="F151" s="33"/>
+      <c r="G151" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="1:8">
+      <c r="A152" s="34"/>
+      <c r="B152" s="34"/>
+      <c r="C152" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D152" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E152" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G152" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:8">
+      <c r="A153" s="34"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="19"/>
+      <c r="D153" s="62"/>
+      <c r="E153" s="21"/>
+      <c r="F153" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G153" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:8">
+      <c r="A154" s="34"/>
+      <c r="B154" s="34"/>
+      <c r="C154" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D154" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="E154" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="F154" s="33"/>
+      <c r="G154" s="16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:8">
+      <c r="A155" s="34"/>
+      <c r="B155" s="34"/>
+      <c r="C155" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D155" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E155" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="1:8">
+      <c r="A156" s="34"/>
+      <c r="B156" s="34"/>
+      <c r="C156" s="19"/>
+      <c r="D156" s="18"/>
+      <c r="E156" s="18"/>
+      <c r="F156" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G156" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="1:8">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D157" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E157" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F157" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G157" s="16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:8">
+      <c r="A158" s="34"/>
+      <c r="B158" s="34"/>
+      <c r="C158" s="34"/>
+      <c r="D158" s="21"/>
+      <c r="E158" s="34"/>
+      <c r="F158" s="19"/>
+      <c r="G158" s="16" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:8">
+      <c r="A159" s="34"/>
+      <c r="B159" s="34"/>
+      <c r="C159" s="34"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="19"/>
+      <c r="F159" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G159" s="16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:8">
+      <c r="A160" s="97">
+        <v>36</v>
+      </c>
+      <c r="B160" s="97" t="s">
+        <v>240</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E160" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:7">
+      <c r="A161" s="98"/>
+      <c r="B161" s="98"/>
+      <c r="C161" s="19"/>
+      <c r="D161" s="18"/>
+      <c r="E161" s="18"/>
+      <c r="F161" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:7">
+      <c r="A162" s="98"/>
+      <c r="B162" s="98"/>
+      <c r="C162" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D162" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="E162" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="F162" s="33"/>
+      <c r="G162" s="16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:7">
+      <c r="A163" s="98"/>
+      <c r="B163" s="98"/>
+      <c r="C163" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D150" s="77" t="s">
-        <v>229</v>
-      </c>
-      <c r="E150" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="F150" s="31"/>
-      <c r="G150" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" spans="1:8">
-      <c r="A151" s="32"/>
-      <c r="B151" s="32"/>
-      <c r="C151" s="14" t="s">
+      <c r="D163" s="91" t="s">
+        <v>241</v>
+      </c>
+      <c r="E163" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="F163" s="33"/>
+      <c r="G163" s="16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:7">
+      <c r="A164" s="98"/>
+      <c r="B164" s="98"/>
+      <c r="C164" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D151" s="57" t="s">
-        <v>230</v>
-      </c>
-      <c r="E151" s="13" t="s">
+      <c r="D164" s="91" t="s">
+        <v>243</v>
+      </c>
+      <c r="E164" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F164" s="33"/>
+      <c r="G164" s="16" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="1:7">
+      <c r="A165" s="98"/>
+      <c r="B165" s="98"/>
+      <c r="C165" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D165" s="91" t="s">
+        <v>245</v>
+      </c>
+      <c r="E165" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F151" s="14" t="s">
+      <c r="F165" s="33"/>
+      <c r="G165" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="1:7">
+      <c r="A166" s="98"/>
+      <c r="B166" s="98"/>
+      <c r="C166" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D166" s="91" t="s">
+        <v>247</v>
+      </c>
+      <c r="E166" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F166" s="33"/>
+      <c r="G166" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="1:7">
+      <c r="A167" s="98"/>
+      <c r="B167" s="98"/>
+      <c r="C167" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D167" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E167" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F167" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G167" s="16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="1:7">
+      <c r="A168" s="98"/>
+      <c r="B168" s="98"/>
+      <c r="C168" s="34"/>
+      <c r="D168" s="21"/>
+      <c r="E168" s="34"/>
+      <c r="F168" s="19"/>
+      <c r="G168" s="16" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="1:7">
+      <c r="A169" s="98"/>
+      <c r="B169" s="98"/>
+      <c r="C169" s="34"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="19"/>
+      <c r="F169" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G169" s="16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="1:7">
+      <c r="A170" s="98"/>
+      <c r="B170" s="98"/>
+      <c r="C170" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D170" s="99" t="s">
+        <v>248</v>
+      </c>
+      <c r="E170" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="F170" s="33">
+        <v>1</v>
+      </c>
+      <c r="G170" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="1:7">
+      <c r="A171" s="15">
+        <v>37</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C171" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="E171" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="G171" s="16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="1:7">
+      <c r="A172" s="34"/>
+      <c r="B172" s="34"/>
+      <c r="C172" s="19"/>
+      <c r="D172" s="21"/>
+      <c r="E172" s="21"/>
+      <c r="F172" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G172" s="21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="1:7">
+      <c r="A173" s="19"/>
+      <c r="B173" s="19"/>
+      <c r="C173" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" s="91" t="s">
+        <v>254</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="F173" s="33"/>
+      <c r="G173" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="1:7">
+      <c r="A174" s="15">
+        <v>38</v>
+      </c>
+      <c r="B174" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C174" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E174" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G174" s="16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="1:7">
+      <c r="A175" s="19"/>
+      <c r="B175" s="19"/>
+      <c r="C175" s="19"/>
+      <c r="D175" s="18"/>
+      <c r="E175" s="18"/>
+      <c r="F175" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G175" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="1:7">
+      <c r="A176" s="15">
+        <v>39</v>
+      </c>
+      <c r="B176" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="C176" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E176" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F176" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G151" s="13" t="s">
+      <c r="G176" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:8">
-      <c r="A152" s="32"/>
-      <c r="B152" s="32"/>
-      <c r="C152" s="18"/>
-      <c r="D152" s="60"/>
-      <c r="E152" s="20"/>
-      <c r="F152" s="14" t="s">
+    <row r="177" customHeight="1" spans="1:7">
+      <c r="A177" s="19"/>
+      <c r="B177" s="78"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="62"/>
+      <c r="E177" s="21"/>
+      <c r="F177" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G152" s="13" t="s">
+      <c r="G177" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:8">
-      <c r="A153" s="32"/>
-      <c r="B153" s="32"/>
-      <c r="C153" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D153" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="E153" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F153" s="31"/>
-      <c r="G153" s="15" t="s">
+    <row r="178" customHeight="1" spans="1:7">
+      <c r="A178" s="15">
+        <v>40</v>
+      </c>
+      <c r="B178" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C178" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D178" s="101" t="s">
+        <v>261</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F178" s="33">
+        <v>1</v>
+      </c>
+      <c r="G178" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="1:7">
+      <c r="A179" s="34"/>
+      <c r="B179" s="34"/>
+      <c r="C179" s="34"/>
+      <c r="D179" s="102"/>
+      <c r="E179" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="F179" s="33">
+        <v>1</v>
+      </c>
+      <c r="G179" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="1:7">
+      <c r="A180" s="34"/>
+      <c r="B180" s="34"/>
+      <c r="C180" s="34"/>
+      <c r="D180" s="102"/>
+      <c r="E180" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F180" s="33">
+        <v>1</v>
+      </c>
+      <c r="G180" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="1:7">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="19"/>
+      <c r="D181" s="103"/>
+      <c r="E181" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F181" s="33">
+        <v>1</v>
+      </c>
+      <c r="G181" s="16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="1:7">
+      <c r="A182" s="34"/>
+      <c r="B182" s="34"/>
+      <c r="C182" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F182" s="33"/>
+      <c r="G182" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:7">
+      <c r="A183" s="34"/>
+      <c r="B183" s="34"/>
+      <c r="C183" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E183" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G183" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="1:7">
+      <c r="A184" s="19"/>
+      <c r="B184" s="19"/>
+      <c r="C184" s="19"/>
+      <c r="D184" s="18"/>
+      <c r="E184" s="18"/>
+      <c r="F184" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G184" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:7">
+      <c r="A185" s="33">
+        <v>41</v>
+      </c>
+      <c r="B185" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="C185" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="91" t="s">
+        <v>266</v>
+      </c>
+      <c r="E185" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="F185" s="33"/>
+      <c r="G185" s="16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:7">
+      <c r="A186" s="33"/>
+      <c r="B186" s="33"/>
+      <c r="C186" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E186" s="23" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="154" customHeight="1" spans="1:8">
-      <c r="A154" s="32"/>
-      <c r="B154" s="32"/>
-      <c r="C154" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E154" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F154" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="G154" s="15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" spans="1:8">
-      <c r="A155" s="18"/>
-      <c r="B155" s="18"/>
-      <c r="C155" s="18"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="17"/>
-      <c r="F155" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="G155" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" spans="1:8">
-      <c r="A156" s="14">
-        <v>36</v>
-      </c>
-      <c r="B156" s="14" t="s">
+      <c r="F186" s="33"/>
+      <c r="G186" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="C156" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E156" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F156" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="G156" s="15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" spans="1:8">
-      <c r="A157" s="32"/>
-      <c r="B157" s="32"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="17"/>
-      <c r="F157" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="G157" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" spans="1:8">
-      <c r="A158" s="32"/>
-      <c r="B158" s="32"/>
-      <c r="C158" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D158" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="E158" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F158" s="31"/>
-      <c r="G158" s="15" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" spans="1:8">
-      <c r="A159" s="32"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D159" s="89" t="s">
-        <v>235</v>
-      </c>
-      <c r="E159" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="F159" s="31"/>
-      <c r="G159" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" spans="1:8">
-      <c r="A160" s="32"/>
-      <c r="B160" s="32"/>
-      <c r="C160" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D160" s="89" t="s">
-        <v>236</v>
-      </c>
-      <c r="E160" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="F160" s="31"/>
-      <c r="G160" s="15" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" spans="1:7">
-      <c r="A161" s="32"/>
-      <c r="B161" s="32"/>
-      <c r="C161" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D161" s="89" t="s">
-        <v>238</v>
-      </c>
-      <c r="E161" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="F161" s="31"/>
-      <c r="G161" s="15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" spans="1:7">
-      <c r="A162" s="18"/>
-      <c r="B162" s="18"/>
-      <c r="C162" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D162" s="89" t="s">
-        <v>240</v>
-      </c>
-      <c r="E162" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="F162" s="31"/>
-      <c r="G162" s="15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" spans="1:7">
-      <c r="A163" s="14">
-        <v>37</v>
-      </c>
-      <c r="B163" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="C163" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="E163" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F163" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G163" s="15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" spans="1:7">
-      <c r="A164" s="32"/>
-      <c r="B164" s="32"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="20"/>
-      <c r="E164" s="20"/>
-      <c r="F164" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G164" s="20" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" spans="1:7">
-      <c r="A165" s="18"/>
-      <c r="B165" s="18"/>
-      <c r="C165" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="89" t="s">
-        <v>245</v>
-      </c>
-      <c r="E165" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="F165" s="31"/>
-      <c r="G165" s="15" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" spans="1:7">
-      <c r="A166" s="31"/>
-      <c r="B166" s="31"/>
-      <c r="C166" s="31"/>
-      <c r="D166" s="95"/>
-      <c r="E166" s="22"/>
-      <c r="F166" s="31"/>
-      <c r="G166" s="15"/>
-    </row>
-    <row r="167" customHeight="1" spans="1:7">
-      <c r="A167" s="31"/>
-      <c r="B167" s="31"/>
-      <c r="C167" s="31"/>
-      <c r="D167" s="95"/>
-      <c r="E167" s="22"/>
-      <c r="F167" s="31"/>
-      <c r="G167" s="15"/>
-    </row>
-    <row r="168" customHeight="1" spans="1:7">
-      <c r="A168" s="31"/>
-      <c r="B168" s="31"/>
-      <c r="C168" s="31"/>
-      <c r="D168" s="95"/>
-      <c r="E168" s="22"/>
-      <c r="F168" s="31"/>
-      <c r="G168" s="15"/>
-    </row>
-    <row r="169" customHeight="1" spans="1:7">
-      <c r="A169" s="31"/>
-      <c r="B169" s="31"/>
-      <c r="C169" s="31"/>
-      <c r="D169" s="95"/>
-      <c r="E169" s="22"/>
-      <c r="F169" s="31"/>
-      <c r="G169" s="15"/>
-    </row>
-    <row r="170" customHeight="1" spans="1:7">
-      <c r="A170" s="31"/>
-      <c r="B170" s="31"/>
-      <c r="C170" s="31"/>
-      <c r="D170" s="95"/>
-      <c r="E170" s="22"/>
-      <c r="F170" s="31"/>
-      <c r="G170" s="15"/>
-    </row>
-    <row r="171" customHeight="1" spans="1:7">
-      <c r="A171" s="31"/>
-      <c r="B171" s="31"/>
-      <c r="C171" s="31"/>
-      <c r="D171" s="95"/>
-      <c r="E171" s="22"/>
-      <c r="F171" s="31"/>
-      <c r="G171" s="15"/>
-    </row>
-    <row r="172" customHeight="1" spans="1:7">
-      <c r="A172" s="31"/>
-      <c r="B172" s="31"/>
-      <c r="C172" s="31"/>
-      <c r="D172" s="95"/>
-      <c r="E172" s="22"/>
-      <c r="F172" s="31"/>
-      <c r="G172" s="15"/>
-    </row>
-    <row r="173" customHeight="1" spans="1:7">
-      <c r="A173" s="31"/>
-      <c r="B173" s="31"/>
-      <c r="C173" s="31"/>
-      <c r="D173" s="95"/>
-      <c r="E173" s="22"/>
-      <c r="F173" s="31"/>
-      <c r="G173" s="15"/>
-    </row>
-    <row r="174" customHeight="1" spans="1:7">
-      <c r="A174" s="31"/>
-      <c r="B174" s="31"/>
-      <c r="C174" s="31"/>
-      <c r="D174" s="95"/>
-      <c r="E174" s="22"/>
-      <c r="F174" s="31"/>
-      <c r="G174" s="15"/>
-    </row>
-    <row r="175" customHeight="1" spans="1:7">
-      <c r="A175" s="31"/>
-      <c r="B175" s="31"/>
-      <c r="C175" s="31"/>
-      <c r="D175" s="95"/>
-      <c r="E175" s="22"/>
-      <c r="F175" s="31"/>
-      <c r="G175" s="15"/>
-    </row>
-    <row r="176" customHeight="1" spans="1:7">
-      <c r="A176" s="31"/>
-      <c r="B176" s="31"/>
-      <c r="C176" s="31"/>
-      <c r="D176" s="95"/>
-      <c r="E176" s="22"/>
-      <c r="F176" s="31"/>
-      <c r="G176" s="15"/>
-    </row>
-    <row r="177" customHeight="1" spans="1:7">
-      <c r="A177" s="31"/>
-      <c r="B177" s="31"/>
-      <c r="C177" s="31"/>
-      <c r="D177" s="95"/>
-      <c r="E177" s="22"/>
-      <c r="F177" s="31"/>
-      <c r="G177" s="15"/>
-    </row>
-    <row r="178" customHeight="1" spans="1:7">
-      <c r="A178" s="31"/>
-      <c r="B178" s="31"/>
-      <c r="C178" s="31"/>
-      <c r="D178" s="95"/>
-      <c r="E178" s="22"/>
-      <c r="F178" s="31"/>
-      <c r="G178" s="15"/>
-    </row>
-    <row r="179" customHeight="1" spans="1:7">
-      <c r="A179" s="31"/>
-      <c r="B179" s="31"/>
-      <c r="C179" s="31"/>
-      <c r="D179" s="95"/>
-      <c r="E179" s="22"/>
-      <c r="F179" s="31"/>
-      <c r="G179" s="15"/>
-    </row>
-    <row r="180" customHeight="1" spans="1:7">
-      <c r="A180" s="31"/>
-      <c r="B180" s="31"/>
-      <c r="C180" s="31"/>
-      <c r="D180" s="95"/>
-      <c r="E180" s="22"/>
-      <c r="F180" s="31"/>
-      <c r="G180" s="15"/>
-    </row>
-    <row r="181" customHeight="1" spans="1:7">
-      <c r="A181" s="31"/>
-      <c r="B181" s="31"/>
-      <c r="C181" s="31"/>
-      <c r="D181" s="95"/>
-      <c r="E181" s="22"/>
-      <c r="F181" s="31"/>
-      <c r="G181" s="15"/>
-    </row>
-    <row r="182" customHeight="1" spans="1:7">
-      <c r="A182" s="31"/>
-      <c r="B182" s="31"/>
-      <c r="C182" s="31"/>
-      <c r="D182" s="95"/>
-      <c r="E182" s="22"/>
-      <c r="F182" s="31"/>
-      <c r="G182" s="15"/>
-    </row>
-    <row r="183" customHeight="1" spans="1:7">
-      <c r="A183" s="31"/>
-      <c r="B183" s="31"/>
-      <c r="C183" s="31"/>
-      <c r="D183" s="95"/>
-      <c r="E183" s="22"/>
-      <c r="F183" s="31"/>
-      <c r="G183" s="15"/>
-    </row>
-    <row r="184" customHeight="1" spans="1:7">
-      <c r="A184" s="31"/>
-      <c r="B184" s="31"/>
-      <c r="C184" s="31"/>
-      <c r="D184" s="95"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="31"/>
-      <c r="G184" s="15"/>
-    </row>
-    <row r="185" customHeight="1" spans="1:7">
-      <c r="A185" s="31"/>
-      <c r="B185" s="31"/>
-      <c r="C185" s="31"/>
-      <c r="D185" s="95"/>
-      <c r="E185" s="22"/>
-      <c r="F185" s="31"/>
-      <c r="G185" s="15"/>
+    </row>
+    <row r="187" customHeight="1" spans="1:7">
+      <c r="A187" s="33"/>
+      <c r="B187" s="33"/>
+      <c r="C187" s="33"/>
+      <c r="D187" s="105"/>
+      <c r="E187" s="23"/>
+      <c r="F187" s="33"/>
+      <c r="G187" s="16"/>
+    </row>
+    <row r="188" customHeight="1" spans="1:7">
+      <c r="A188" s="33"/>
+      <c r="B188" s="33"/>
+      <c r="C188" s="33"/>
+      <c r="D188" s="105"/>
+      <c r="E188" s="23"/>
+      <c r="F188" s="33"/>
+      <c r="G188" s="16"/>
+    </row>
+    <row r="189" customHeight="1" spans="1:7">
+      <c r="A189" s="33"/>
+      <c r="B189" s="33"/>
+      <c r="C189" s="33"/>
+      <c r="D189" s="105"/>
+      <c r="E189" s="23"/>
+      <c r="F189" s="33"/>
+      <c r="G189" s="16"/>
+    </row>
+    <row r="190" customHeight="1" spans="1:7">
+      <c r="A190" s="33"/>
+      <c r="B190" s="33"/>
+      <c r="C190" s="33"/>
+      <c r="D190" s="105"/>
+      <c r="E190" s="23"/>
+      <c r="F190" s="33"/>
+      <c r="G190" s="16"/>
+    </row>
+    <row r="191" customHeight="1" spans="1:7">
+      <c r="A191" s="33"/>
+      <c r="B191" s="33"/>
+      <c r="C191" s="33"/>
+      <c r="D191" s="105"/>
+      <c r="E191" s="23"/>
+      <c r="F191" s="33"/>
+      <c r="G191" s="16"/>
+    </row>
+    <row r="192" customHeight="1" spans="1:7">
+      <c r="A192" s="33"/>
+      <c r="B192" s="33"/>
+      <c r="C192" s="33"/>
+      <c r="D192" s="105"/>
+      <c r="E192" s="23"/>
+      <c r="F192" s="33"/>
+      <c r="G192" s="16"/>
+    </row>
+    <row r="193" customHeight="1" spans="1:7">
+      <c r="A193" s="33"/>
+      <c r="B193" s="33"/>
+      <c r="C193" s="33"/>
+      <c r="D193" s="105"/>
+      <c r="E193" s="23"/>
+      <c r="F193" s="33"/>
+      <c r="G193" s="16"/>
+    </row>
+    <row r="194" customHeight="1" spans="1:7">
+      <c r="A194" s="33"/>
+      <c r="B194" s="33"/>
+      <c r="C194" s="33"/>
+      <c r="D194" s="105"/>
+      <c r="E194" s="23"/>
+      <c r="F194" s="33"/>
+      <c r="G194" s="16"/>
+    </row>
+    <row r="195" customHeight="1" spans="1:7">
+      <c r="A195" s="33"/>
+      <c r="B195" s="33"/>
+      <c r="C195" s="33"/>
+      <c r="D195" s="105"/>
+      <c r="E195" s="23"/>
+      <c r="F195" s="33"/>
+      <c r="G195" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="241">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A11:A18"/>
@@ -6812,10 +7216,13 @@
     <mergeCell ref="A130:A135"/>
     <mergeCell ref="A137:A139"/>
     <mergeCell ref="A140:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A148:A155"/>
-    <mergeCell ref="A156:A162"/>
-    <mergeCell ref="A163:A165"/>
+    <mergeCell ref="A145:A148"/>
+    <mergeCell ref="A149:A159"/>
+    <mergeCell ref="A160:A170"/>
+    <mergeCell ref="A171:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A184"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="B11:B18"/>
@@ -6845,10 +7252,13 @@
     <mergeCell ref="B130:B135"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B140:B144"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B155"/>
-    <mergeCell ref="B156:B162"/>
-    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="B145:B148"/>
+    <mergeCell ref="B149:B159"/>
+    <mergeCell ref="B160:B170"/>
+    <mergeCell ref="B171:B173"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="B178:B184"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="C11:C12"/>
@@ -6895,10 +7305,16 @@
     <mergeCell ref="C141:C142"/>
     <mergeCell ref="C143:C144"/>
     <mergeCell ref="C145:C146"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C163:C164"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="C155:C156"/>
+    <mergeCell ref="C157:C159"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="C167:C169"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="C183:C184"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D11:D12"/>
@@ -6942,10 +7358,16 @@
     <mergeCell ref="D141:D142"/>
     <mergeCell ref="D143:D144"/>
     <mergeCell ref="D145:D146"/>
-    <mergeCell ref="D151:D152"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="D163:D164"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="D167:D169"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D183:D184"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E11:E12"/>
@@ -6989,10 +7411,17 @@
     <mergeCell ref="E141:E142"/>
     <mergeCell ref="E143:E144"/>
     <mergeCell ref="E145:E146"/>
-    <mergeCell ref="E151:E152"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="E156:E157"/>
-    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="E155:E156"/>
+    <mergeCell ref="E157:E159"/>
+    <mergeCell ref="E160:E161"/>
+    <mergeCell ref="E167:E169"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="E176:E177"/>
+    <mergeCell ref="E183:E184"/>
+    <mergeCell ref="F157:F158"/>
+    <mergeCell ref="F167:F168"/>
     <mergeCell ref="G88:G92"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H11:H26"/>
@@ -7009,432 +7438,476 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88333333333333" style="10" customWidth="1"/>
+    <col min="1" max="1" width="8.88333333333333" style="11" customWidth="1"/>
     <col min="2" max="2" width="29.8833333333333" style="9" customWidth="1"/>
-    <col min="3" max="3" width="20.3833333333333" style="10" customWidth="1"/>
+    <col min="3" max="3" width="32.125" style="11" customWidth="1"/>
     <col min="4" max="4" width="17" style="9" customWidth="1"/>
-    <col min="5" max="5" width="68.5" style="9" customWidth="1"/>
-    <col min="6" max="6" width="35.1333333333333" style="9" customWidth="1"/>
+    <col min="5" max="5" width="73.875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="42.625" style="9" customWidth="1"/>
     <col min="7" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A1" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="E2" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="15" t="s">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="19"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F4" s="19"/>
+      <c r="E4" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="15" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="19"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="19"/>
+      <c r="E6" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="19"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="19"/>
+      <c r="E8" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="15" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="19"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>5</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="19"/>
+      <c r="E10" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="15" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="19"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>6</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="19"/>
+      <c r="E12" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="15" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="19"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A14" s="20">
+      <c r="A14" s="21">
         <v>7</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F14" s="19"/>
+      <c r="E14" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="15" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="21"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A16" s="17">
+      <c r="A16" s="18">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="22" t="s">
+      <c r="B16" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="22"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A17" s="20">
+      <c r="A17" s="21">
         <v>9</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F17" s="23" t="s">
+      <c r="E17" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F17" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="15" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="24"/>
+      <c r="F18" s="25"/>
     </row>
     <row r="19" s="9" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A19" s="22">
+      <c r="A19" s="23">
         <v>10</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <v>1</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>259</v>
+      <c r="E19" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:6">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>11</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="B20" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="F20" s="22"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F20" s="23"/>
     </row>
     <row r="21" customHeight="1" spans="1:6">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="22" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" s="22"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F21" s="23"/>
     </row>
     <row r="22" customHeight="1" spans="1:6">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>12</v>
       </c>
-      <c r="B22" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22" s="22"/>
+      <c r="B22" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="F22" s="23"/>
     </row>
     <row r="23" customHeight="1" spans="1:6">
-      <c r="A23" s="17"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="F23" s="22"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="22"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:6">
-      <c r="A25" s="22"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="F25" s="15"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="23"/>
+    </row>
+    <row r="24" s="10" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A24" s="26">
+        <v>13</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" s="10" customFormat="1" ht="28" customHeight="1" spans="1:6">
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" customHeight="1" spans="1:6">
-      <c r="A26" s="22"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" customHeight="1" spans="1:6">
-      <c r="A27" s="22"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
-      <c r="A28" s="22"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
-      <c r="A29" s="22"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
-      <c r="A30" s="22"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:6">
+      <c r="A31" s="23"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:6">
+      <c r="A32" s="23"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="23"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:6">
+      <c r="A34" s="23"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="34">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7445,6 +7918,7 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B6:B7"/>
@@ -7455,6 +7929,7 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C7"/>
@@ -7466,6 +7941,7 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="F2:F15"/>
     <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F24:F25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7489,7 +7965,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7502,45 +7978,45 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="5" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="6" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="E3" s="6">
         <v>322</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="7" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>7</v>
@@ -7548,189 +8024,189 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B4" s="6">
         <v>44</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="6" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="E4" s="6">
         <v>344</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="7" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="H4" s="7">
         <v>22</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="B5" s="6">
         <v>66</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="6" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="E5" s="6">
         <v>366</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="7" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="H5" s="7">
         <v>25</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="B6" s="6">
         <v>88</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="6" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="E6" s="6">
         <v>388</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="7" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="H6" s="7">
         <v>28</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="B7" s="6">
         <v>88</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="6" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="E7" s="6">
         <v>388</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="7" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="H7" s="7">
         <v>30</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="B8" s="6">
         <v>110</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="6" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="E8" s="6">
         <v>410</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="7" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="H8" s="7">
         <v>35</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="B9" s="6">
         <v>132</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="6" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E9" s="6">
         <v>432</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="7" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="H9" s="7">
         <v>35</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="B10" s="6">
         <v>154</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="6" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="E10" s="6">
         <v>454</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="7" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="H10" s="7">
         <v>35</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="B11" s="6">
         <v>165</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="6" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="E11" s="6">
         <v>465</v>
@@ -7742,14 +8218,14 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="B12" s="6">
         <v>165</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="6" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="E12" s="6">
         <v>465</v>
@@ -7761,14 +8237,14 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="B13" s="6">
         <v>187</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="6" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="E13" s="6">
         <v>487</v>
@@ -7780,14 +8256,14 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="B14" s="6">
         <v>209</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="6" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="E14" s="6">
         <v>509</v>
@@ -7799,14 +8275,14 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="B15" s="6">
         <v>231</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="E15" s="6">
         <v>531</v>
@@ -7818,14 +8294,14 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="B16" s="6">
         <v>253</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="6" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="E16" s="6">
         <v>553</v>
@@ -7837,14 +8313,14 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="B17" s="6">
         <v>253</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="6" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="E17" s="6">
         <v>553</v>
@@ -7856,14 +8332,14 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="B18" s="6">
         <v>275</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="6" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="E18" s="6">
         <v>575</v>
@@ -7875,14 +8351,14 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B19" s="6">
         <v>297</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="6" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="E19" s="6">
         <v>597</v>
@@ -7894,14 +8370,14 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="B20" s="6">
         <v>300</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="6" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="E20" s="6">
         <v>600</v>
@@ -7913,14 +8389,14 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B21" s="6">
         <v>300</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="6" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="E21" s="6">
         <v>600</v>
@@ -7932,14 +8408,14 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="B22" s="6">
         <v>300</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="6" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E22" s="6">
         <v>600</v>
